--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -542,6 +542,106 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Balaji P</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21:41:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Balaji P</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21:44:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Balaji P</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>22:37:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Balaji P</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>22:40:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Balaji P</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>22:41:12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -642,6 +642,26 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Balaji P</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10:56:12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
